--- a/results/block3_results/segment stenosis/Normal_2/stenosis_summary_Normal_2.xlsx
+++ b/results/block3_results/segment stenosis/Normal_2/stenosis_summary_Normal_2.xlsx
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>97.09260018453763</v>
+        <v>93.94116395779251</v>
       </c>
       <c r="F2" t="n">
         <v>4</v>
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>93.22655280984159</v>
+        <v>90.14057811460118</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
@@ -546,30 +546,30 @@
         <v>471</v>
       </c>
       <c r="I3" t="n">
-        <v>327</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Proximal RCA</t>
+          <t>Proximal LCX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RCA</t>
+          <t>LCA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>RCA</t>
+          <t>LCX</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>77.18920566901018</v>
+        <v>78.10357840320319</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
@@ -580,19 +580,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>259</v>
+        <v>632</v>
       </c>
       <c r="I4" t="n">
-        <v>184</v>
+        <v>632</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Proximal LCX</t>
+          <t>LCX posterolateral branch</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>77.07747077631713</v>
+        <v>77.96856518034964</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -617,33 +617,33 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>632</v>
+        <v>792</v>
       </c>
       <c r="I5" t="n">
-        <v>632</v>
+        <v>728</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LCX posterolateral branch</t>
+          <t>Proximal RCA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LCA</t>
+          <t>RCA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LCX</t>
+          <t>RCA</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>76.76616129235144</v>
+        <v>71.52196268718048</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
@@ -654,56 +654,56 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>792</v>
+        <v>259</v>
       </c>
       <c r="I6" t="n">
-        <v>763</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mid RCA</t>
+          <t>Distal LAD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RCA</t>
+          <t>LCA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>RCA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>73.34886027528022</v>
+        <v>67.81264134577366</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Severe stenosis</t>
+          <t>Moderate stenosis</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>698</v>
+        <v>577</v>
       </c>
       <c r="I7" t="n">
-        <v>698</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Second diagonal (D2)</t>
+          <t>Distal LCX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -713,11 +713,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LCX</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>67.32217751427825</v>
+        <v>62.21685031125167</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
@@ -728,33 +728,33 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>83</v>
+        <v>614</v>
       </c>
       <c r="I8" t="n">
-        <v>48</v>
+        <v>519</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Distal LCX</t>
+          <t>Mid RCA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LCA</t>
+          <t>RCA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LCX</t>
+          <t>RCA</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>64.47148623624821</v>
+        <v>59.6439378950183</v>
       </c>
       <c r="F9" t="n">
         <v>3</v>
@@ -765,33 +765,33 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>614</v>
+        <v>698</v>
       </c>
       <c r="I9" t="n">
-        <v>579</v>
+        <v>698</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Distal RCA</t>
+          <t>Mid LAD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RCA</t>
+          <t>LCA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>RCA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>62.35848794919296</v>
+        <v>57.78675001947619</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
@@ -802,33 +802,33 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>577</v>
+        <v>358</v>
       </c>
       <c r="I10" t="n">
-        <v>502</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Distal LAD</t>
+          <t>Distal RCA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LCA</t>
+          <t>RCA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>RCA</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>55.46926195631712</v>
+        <v>53.97862554491246</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>
@@ -842,16 +842,16 @@
         <v>577</v>
       </c>
       <c r="I11" t="n">
-        <v>547</v>
+        <v>439</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mid LAD</t>
+          <t>Second diagonal (D2)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -865,21 +865,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53.99143325328575</v>
+        <v>45.89948455234406</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Moderate stenosis</t>
+          <t>Mild stenosis</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>358</v>
+        <v>83</v>
       </c>
       <c r="I12" t="n">
-        <v>358</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -902,21 +902,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>49.71907711687957</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Mild stenosis</t>
+          <t>No visible stenosis</t>
         </is>
       </c>
       <c r="H13" t="n">
         <v>499</v>
       </c>
       <c r="I13" t="n">
-        <v>352</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
